--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_09-07-2026.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_09-07-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Recticel_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D021F6AB-25CA-4CA7-A9C1-7E919284D7AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8E41A96-2005-4D1E-8201-E6C48BBAA8D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2715" yWindow="585" windowWidth="21600" windowHeight="12750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29190" yWindow="390" windowWidth="21600" windowHeight="12750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -787,34 +787,34 @@
     <t>£126.96</t>
   </si>
   <si>
-    <t>£161.40</t>
-  </si>
-  <si>
     <t>£122.43</t>
   </si>
   <si>
-    <t>£131.38</t>
-  </si>
-  <si>
     <t>£657.00</t>
   </si>
   <si>
-    <t>£726.25</t>
-  </si>
-  <si>
-    <t>£729.35</t>
-  </si>
-  <si>
     <t>£711.4</t>
   </si>
   <si>
-    <t>£719.08</t>
-  </si>
-  <si>
     <t>£705.95</t>
   </si>
   <si>
     <t>£716.05</t>
+  </si>
+  <si>
+    <t>£106.99</t>
+  </si>
+  <si>
+    <t>£91.99</t>
+  </si>
+  <si>
+    <t>£594.55</t>
+  </si>
+  <si>
+    <t>£659.55</t>
+  </si>
+  <si>
+    <t>£559.96</t>
   </si>
 </sst>
 </file>
@@ -2176,7 +2176,7 @@
         <v>254</v>
       </c>
       <c r="O18" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="P18" t="s">
         <v>29</v>
@@ -2229,10 +2229,10 @@
         <v>26</v>
       </c>
       <c r="N19" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O19" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="P19" t="s">
         <v>29</v>
@@ -2444,7 +2444,7 @@
         <v>26</v>
       </c>
       <c r="K23" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="L23" t="s">
         <v>26</v>
@@ -2453,10 +2453,10 @@
         <v>218</v>
       </c>
       <c r="N23" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="O23" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="P23" t="s">
         <v>26</v>
@@ -2500,7 +2500,7 @@
         <v>26</v>
       </c>
       <c r="K24" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="L24" t="s">
         <v>26</v>
@@ -2509,10 +2509,10 @@
         <v>29</v>
       </c>
       <c r="N24" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="O24" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="P24" t="s">
         <v>26</v>
@@ -2565,10 +2565,10 @@
         <v>29</v>
       </c>
       <c r="N25" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="O25" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="P25" t="s">
         <v>26</v>
